--- a/output/catalog.xlsx
+++ b/output/catalog.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,6 +430,18 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hunter supplier for unknown</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
